--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121150679</v>
       </c>
       <c r="B3" t="n">
-        <v>91443</v>
+        <v>91453</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>121150678</v>
       </c>
       <c r="B4" t="n">
-        <v>90458</v>
+        <v>90468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>121150680</v>
       </c>
       <c r="B5" t="n">
-        <v>91478</v>
+        <v>91488</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150679</v>
+        <v>121150680</v>
       </c>
       <c r="B3" t="n">
-        <v>91453</v>
+        <v>91488</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504091</v>
+        <v>504098</v>
       </c>
       <c r="R3" t="n">
-        <v>6623791</v>
+        <v>6623799</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150680</v>
+        <v>121150679</v>
       </c>
       <c r="B5" t="n">
-        <v>91488</v>
+        <v>91453</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1034,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504098</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>6623799</v>
+        <v>6623791</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150680</v>
+        <v>121150678</v>
       </c>
       <c r="B3" t="n">
-        <v>91488</v>
+        <v>90480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504098</v>
+        <v>504257</v>
       </c>
       <c r="R3" t="n">
-        <v>6623799</v>
+        <v>6623941</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150678</v>
+        <v>121150680</v>
       </c>
       <c r="B4" t="n">
-        <v>90468</v>
+        <v>91500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>2014</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504257</v>
+        <v>504098</v>
       </c>
       <c r="R4" t="n">
-        <v>6623941</v>
+        <v>6623799</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,7 +1021,7 @@
         <v>121150679</v>
       </c>
       <c r="B5" t="n">
-        <v>91453</v>
+        <v>91465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150678</v>
+        <v>121150680</v>
       </c>
       <c r="B3" t="n">
-        <v>90480</v>
+        <v>91501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504257</v>
+        <v>504098</v>
       </c>
       <c r="R3" t="n">
-        <v>6623941</v>
+        <v>6623799</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150680</v>
+        <v>121150678</v>
       </c>
       <c r="B4" t="n">
-        <v>91500</v>
+        <v>90481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2014</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504098</v>
+        <v>504257</v>
       </c>
       <c r="R4" t="n">
-        <v>6623799</v>
+        <v>6623941</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,7 +1021,7 @@
         <v>121150679</v>
       </c>
       <c r="B5" t="n">
-        <v>91465</v>
+        <v>91466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150680</v>
+        <v>121150679</v>
       </c>
       <c r="B3" t="n">
-        <v>91501</v>
+        <v>91469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504098</v>
+        <v>504091</v>
       </c>
       <c r="R3" t="n">
-        <v>6623799</v>
+        <v>6623791</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -910,7 +910,7 @@
         <v>121150678</v>
       </c>
       <c r="B4" t="n">
-        <v>90481</v>
+        <v>90484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150679</v>
+        <v>121150680</v>
       </c>
       <c r="B5" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1034,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504098</v>
       </c>
       <c r="R5" t="n">
-        <v>6623791</v>
+        <v>6623799</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44794-2024 artfynd.xlsx
+++ b/artfynd/A 44794-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150679</v>
+        <v>121150680</v>
       </c>
       <c r="B3" t="n">
-        <v>91469</v>
+        <v>91504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504091</v>
+        <v>504098</v>
       </c>
       <c r="R3" t="n">
-        <v>6623791</v>
+        <v>6623799</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150680</v>
+        <v>121150679</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1034,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504098</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>6623799</v>
+        <v>6623791</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
